--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487163_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487163_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7933</v>
+        <v>3.4161</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2172</v>
+        <v>2.3754</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5761</v>
+        <v>1.0407</v>
       </c>
       <c r="G2" t="n">
         <v>-2.1161</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4713</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5897</v>
+        <v>-0.2521</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8817</v>
+        <v>0.3463</v>
       </c>
       <c r="V2" t="n">
         <v>6.017</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9194</v>
+        <v>3.1325</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3319</v>
+        <v>3.4916</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4126</v>
+        <v>-0.359</v>
       </c>
       <c r="G3" t="n">
         <v>1.9634</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5579</v>
+        <v>-0.3447</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5208</v>
+        <v>-0.3612</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.037</v>
+        <v>0.0165</v>
       </c>
       <c r="V3" t="n">
         <v>1.5138</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.18</v>
+        <v>0.8597</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3223</v>
+        <v>0.9218</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1423</v>
+        <v>-0.062</v>
       </c>
       <c r="G4" t="n">
         <v>0.2513</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1567</v>
+        <v>-0.1636</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3702</v>
+        <v>-0.0304</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2135</v>
+        <v>-0.1332</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. KONE FEZING</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-0.7171</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6836</v>
+        <v>-1.7267</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3109</v>
+        <v>1.0096</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4433</v>
+        <v>-0.3801</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0577</v>
+        <v>1.2429</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3856</v>
+        <v>-1.623</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7563</v>
+        <v>0.3396</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.797</v>
+        <v>0.9829</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>-0.6433</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.7197</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2607</v>
+        <v>0.26</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4263</v>
+        <v>-0.9797</v>
       </c>
       <c r="P5" t="n">
-        <v>0.965</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5162</v>
+        <v>-0.2142</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0727</v>
+        <v>-0.7079</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.589</v>
+        <v>0.4937</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6945</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>F. KONE FEZING</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2644</v>
+        <v>-1.1085</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3275</v>
+        <v>-0.8244</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0631</v>
+        <v>-0.2841</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3801</v>
+        <v>-1.4433</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2429</v>
+        <v>-1.0577</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.623</v>
+        <v>-0.3856</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3396</v>
+        <v>-0.7563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9829</v>
+        <v>-0.797</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6433</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7197</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.26</v>
+        <v>-0.2607</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9797</v>
+        <v>-0.4263</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7615</v>
+        <v>-0.6303</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3087</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5473</v>
+        <v>-0.5622</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5912</v>
+        <v>-1.3304</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7204</v>
+        <v>-2.6203</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1292</v>
+        <v>1.2898</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0778</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3979</v>
+        <v>-0.1372</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4019</v>
+        <v>-0.3017</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004</v>
+        <v>0.1646</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0806</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9011</v>
+        <v>-2.035</v>
       </c>
       <c r="E8" t="n">
         <v>0.5809</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.482</v>
+        <v>-2.6158</v>
       </c>
       <c r="G8" t="n">
         <v>-3.6382</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2386</v>
+        <v>0.1048</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2247</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4633</v>
+        <v>0.3295</v>
       </c>
       <c r="V8" t="n">
         <v>0.5334</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1072</v>
+        <v>-2.2327</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2824</v>
+        <v>0.3779</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8248</v>
+        <v>-2.6106</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1331</v>
@@ -1156,13 +1156,13 @@
         <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6234</v>
+        <v>-0.7489</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3537</v>
+        <v>-0.6933</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2697</v>
+        <v>-0.0556</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3508</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1259</v>
+        <v>-2.7789</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7931</v>
+        <v>-0.6335</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3328</v>
+        <v>-2.1454</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1959</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.123</v>
+        <v>-0.776</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5803</v>
+        <v>-0.4207</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5427</v>
+        <v>-0.3553</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0916</v>
+        <v>-2.7943</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6453</v>
+        <v>1.9427</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.737000000000002</v>
+        <v>-4.736800000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-8.7698</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8019000000000001</v>
+        <v>0.8018999999999996</v>
       </c>
       <c r="I11" t="n">
         <v>-9.5715</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6345999999999999</v>
+        <v>-0.6345999999999991</v>
       </c>
       <c r="K11" t="n">
         <v>0.6040000000000001</v>
@@ -1312,22 +1312,22 @@
         <v>11.5803</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.1133</v>
+        <v>-2.8159</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.3575</v>
+        <v>-3.0601</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2444000000000001</v>
+        <v>0.2443</v>
       </c>
       <c r="V11" t="n">
-        <v>5.896</v>
+        <v>5.896000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>14.3229</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.4269</v>
+        <v>-8.426900000000002</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.6586</v>
+        <v>6.4931</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7181</v>
+        <v>5.4191</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9406</v>
+        <v>1.0741</v>
       </c>
       <c r="G12" t="n">
         <v>3.9443</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7416</v>
+        <v>0.0929</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0562</v>
+        <v>-0.3552</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3146</v>
+        <v>0.4481</v>
       </c>
       <c r="V12" t="n">
         <v>2.4559</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2213</v>
+        <v>2.8297</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4404</v>
+        <v>2.5406</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2192</v>
+        <v>0.2891</v>
       </c>
       <c r="G13" t="n">
         <v>6.109</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1084</v>
+        <v>0.5</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.078</v>
+        <v>0.0222</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0304</v>
+        <v>0.4779</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2702</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4348</v>
+        <v>2.343</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9299</v>
+        <v>2.7311</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4952</v>
+        <v>-0.3881</v>
       </c>
       <c r="G14" t="n">
         <v>1.7421</v>
@@ -1546,13 +1546,13 @@
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0721</v>
+        <v>-0.1639</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3682</v>
+        <v>-0.5671</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2961</v>
+        <v>0.4032</v>
       </c>
       <c r="V14" t="n">
         <v>0.5717</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2887</v>
+        <v>-0.8189</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3942</v>
+        <v>-3.1402</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6829</v>
+        <v>2.3214</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.254</v>
+        <v>-0.4948</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2379</v>
+        <v>-1.8786</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4919</v>
+        <v>1.3838</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0138</v>
+        <v>-1.4562</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6052999999999999</v>
+        <v>-2.3187</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.619</v>
+        <v>0.8625</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2403</v>
+        <v>0.9614</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3674</v>
+        <v>0.4401</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1271</v>
+        <v>0.5212</v>
       </c>
       <c r="P15" t="n">
-        <v>0.579</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.193</v>
+        <v>-3.0881</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8422</v>
+        <v>0.278</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6009</v>
+        <v>-0.4379</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2413</v>
+        <v>0.7158</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4559</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4559</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3524</v>
+        <v>-0.9296</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2598</v>
+        <v>0.5931</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6121</v>
+        <v>-1.5226</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6258</v>
+        <v>-0.254</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9936</v>
+        <v>0.2379</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3677</v>
+        <v>-0.4919</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.659</v>
+        <v>-0.0138</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6262</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0328</v>
+        <v>-0.619</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0332</v>
+        <v>-0.2403</v>
       </c>
       <c r="N16" t="n">
         <v>-0.3674</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4006</v>
+        <v>0.1271</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4013</v>
+        <v>1.2014</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9188</v>
+        <v>0.7998</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4825</v>
+        <v>0.4015</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5138</v>
+        <v>-2.4559</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5138</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4913</v>
+        <v>-0.9671</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8398</v>
+        <v>-0.1408</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3485</v>
+        <v>-0.8263</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4948</v>
+        <v>-0.6258</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8786</v>
+        <v>-0.9936</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3838</v>
+        <v>0.3677</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4562</v>
+        <v>-0.659</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.3187</v>
+        <v>-0.6262</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8625</v>
+        <v>-0.0328</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9614</v>
+        <v>0.0332</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4401</v>
+        <v>-0.3674</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5212</v>
+        <v>0.4006</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6055</v>
+        <v>0.7866</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1374</v>
+        <v>0.5182</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7429</v>
+        <v>0.2683</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9421</v>
+        <v>-1.5138</v>
       </c>
       <c r="W17" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8999</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.946</v>
+        <v>-1.1264</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1634</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1094</v>
+        <v>-1.1897</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9706</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6736</v>
+        <v>0.4931</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0727</v>
+        <v>-0.0274</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6008</v>
+        <v>0.5205</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0328</v>
+        <v>-1.6277</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.095</v>
+        <v>-1.3954</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0622</v>
+        <v>-0.2323</v>
       </c>
       <c r="G19" t="n">
         <v>1.0736</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0516</v>
+        <v>0.4567</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4891</v>
+        <v>0.1887</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5625</v>
+        <v>0.268</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1118</v>
+        <v>-2.4369</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2341</v>
+        <v>-1.9337</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8777</v>
+        <v>-0.5033</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7541</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5387</v>
+        <v>0.1362</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6861</v>
+        <v>-0.3856</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1474</v>
+        <v>0.5218</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1701</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.0917</v>
+        <v>3.759200000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>4.7369</v>
+        <v>4.736999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6452</v>
+        <v>-0.9777000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>8.7697</v>
@@ -2062,19 +2062,19 @@
         <v>-0.8018999999999998</v>
       </c>
       <c r="I21" t="n">
-        <v>9.571399999999999</v>
+        <v>9.571400000000001</v>
       </c>
       <c r="J21" t="n">
         <v>8.1348</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1976999999999998</v>
+        <v>-0.1977000000000002</v>
       </c>
       <c r="L21" t="n">
         <v>8.3329</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6349000000000001</v>
+        <v>0.6349</v>
       </c>
       <c r="N21" t="n">
         <v>-0.6041000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>8.6854</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1134</v>
+        <v>3.781</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2444000000000003</v>
+        <v>-0.2443</v>
       </c>
       <c r="U21" t="n">
-        <v>3.3577</v>
+        <v>4.0251</v>
       </c>
       <c r="V21" t="n">
         <v>-5.8963</v>
